--- a/T41_V012_Files/T41_V012_Design_Documents/T41_V12.6_I2C_Assignments.xlsx
+++ b/T41_V012_Files/T41_V012_Design_Documents/T41_V12.6_I2C_Assignments.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\GitHub\T41\T41_V012_Files\T41_V012_Design_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D19CE9-72FB-489B-A75E-9AAD5949F93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C04B87-7219-47FB-AE81-B9FEE998E55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="231">
   <si>
     <t>I2C Addresses For The T41 V012.6</t>
   </si>
@@ -89,9 +89,6 @@
     <t>Wire</t>
   </si>
   <si>
-    <t>19-20</t>
-  </si>
-  <si>
     <t>RFControl</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>Display</t>
   </si>
   <si>
-    <t>0x40/0x38</t>
-  </si>
-  <si>
     <t>Touch Screen Controller</t>
   </si>
   <si>
@@ -168,9 +162,6 @@
   </si>
   <si>
     <t>Si5351a Frequency Control - Primary Receiver and Transmitter</t>
-  </si>
-  <si>
-    <t>0x61/0x6F</t>
   </si>
   <si>
     <t>Si5351a Frequency Control - Second Receiver</t>
@@ -476,15 +467,9 @@
     </r>
   </si>
   <si>
-    <t>0x60/ 0x61/ 0x6F</t>
-  </si>
-  <si>
     <t>Si5351a</t>
   </si>
   <si>
-    <t xml:space="preserve"> Frequency Control - Primary Receiver and Transmitter (0x60), Second Receiver (0x61 or 0x6F)</t>
-  </si>
-  <si>
     <t>RC-0.5 dB Receive Signal Reduction ["1"=On, "0"= Off]</t>
   </si>
   <si>
@@ -506,9 +491,6 @@
     <t>N/C</t>
   </si>
   <si>
-    <t>MF or HF Select - "1"=MF, "0"=HF</t>
-  </si>
-  <si>
     <t>TC-0.5 dB Transmit Power Reduction ["1"=On, "0"= Off]</t>
   </si>
   <si>
@@ -533,9 +515,6 @@
     <t>BPF Board - I2C Addresses</t>
   </si>
   <si>
-    <t>BPF #1</t>
-  </si>
-  <si>
     <t>High = 12M</t>
   </si>
   <si>
@@ -611,9 +590,6 @@
     <t>High = 15M</t>
   </si>
   <si>
-    <t>BPF #2</t>
-  </si>
-  <si>
     <t>LPF Board - I2C Addresses</t>
   </si>
   <si>
@@ -674,12 +650,6 @@
     <t>MCP23017 for Band LPF Selection 160M-6M+Bypass, 1-4 Antenna Selection, XVTR Selection, 100W Module Selection, BPF TX &amp; RX Selection.</t>
   </si>
   <si>
-    <t>0x27/ 0x23</t>
-  </si>
-  <si>
-    <t>111/ 011</t>
-  </si>
-  <si>
     <t>ATU Module - I2C Addresses</t>
   </si>
   <si>
@@ -747,13 +717,43 @@
   </si>
   <si>
     <t>C8 - 2000pF</t>
+  </si>
+  <si>
+    <t>18-19</t>
+  </si>
+  <si>
+    <t>BPF FOR RX  #1</t>
+  </si>
+  <si>
+    <t>BPF FOR RX #2</t>
+  </si>
+  <si>
+    <t>RX #1</t>
+  </si>
+  <si>
+    <t>RX #2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Frequency Control - Receiver and Transmitter (0x60)</t>
+  </si>
+  <si>
+    <t>DEVICE</t>
+  </si>
+  <si>
+    <t>0x61 or 0x6F</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Frequency Control - Second Receiver (0x61 or 0x6F)</t>
+  </si>
+  <si>
+    <t>0x40 or 0x38</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -844,6 +844,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -871,7 +877,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -931,6 +937,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1362,10 +1374,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>19</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1374,10 +1386,10 @@
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="M6" s="10" t="s">
         <v>15</v>
@@ -1385,13 +1397,13 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>23</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>24</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -1405,13 +1417,13 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="9" t="s">
         <v>26</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>27</v>
       </c>
       <c r="E8" s="1">
         <v>7</v>
@@ -1436,13 +1448,13 @@
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="1">
         <v>7</v>
@@ -1451,13 +1463,13 @@
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>29</v>
+        <v>230</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M10" s="10"/>
     </row>
@@ -1474,13 +1486,13 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -1489,13 +1501,13 @@
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>15</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M12" s="10" t="s">
         <v>15</v>
@@ -1503,17 +1515,17 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D13" s="9"/>
       <c r="G13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="M13" s="10"/>
     </row>
@@ -1521,13 +1533,13 @@
       <c r="A14" s="5"/>
       <c r="D14" s="9"/>
       <c r="G14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="M14" s="10"/>
     </row>
@@ -1544,13 +1556,13 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -1559,43 +1571,43 @@
         <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D17" s="9"/>
       <c r="G17" s="1" t="s">
-        <v>45</v>
+        <v>228</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D18" s="9"/>
       <c r="G18" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H18" s="1">
         <v>111</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D19" s="9"/>
       <c r="G19" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1610,13 +1622,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" s="1">
         <v>7</v>
@@ -1625,26 +1637,26 @@
         <v>5</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="D22" s="9"/>
       <c r="G22" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H22" s="1">
         <v>110</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1659,13 +1671,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E24" s="1">
         <v>7</v>
@@ -1674,27 +1686,27 @@
         <v>5</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1709,13 +1721,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -1724,10 +1736,10 @@
         <v>3</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1742,13 +1754,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E29" s="1">
         <v>7</v>
@@ -1757,24 +1769,24 @@
         <v>5</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1789,13 +1801,13 @@
     </row>
     <row r="32" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E32" s="1">
         <v>7</v>
@@ -1804,27 +1816,27 @@
         <v>5</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1839,7 +1851,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1864,7 +1876,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -1890,10 +1902,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
@@ -1921,10 +1933,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="18">
         <v>7</v>
@@ -1933,24 +1945,24 @@
         <v>5</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H6" s="18" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="18" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="18">
         <v>7</v>
@@ -1959,18 +1971,18 @@
         <v>5</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1996,7 +2008,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="16" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -2025,10 +2037,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2065,10 +2077,10 @@
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1">
         <v>5</v>
@@ -2077,16 +2089,16 @@
         <v>7</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2095,19 +2107,19 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2116,10 +2128,10 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2131,10 +2143,10 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2146,10 +2158,10 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2161,10 +2173,10 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2176,10 +2188,10 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2191,10 +2203,10 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2206,10 +2218,10 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2221,10 +2233,10 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2236,10 +2248,10 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2251,10 +2263,10 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2266,10 +2278,10 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2281,10 +2293,10 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2296,10 +2308,10 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2311,10 +2323,10 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2326,10 +2338,10 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2338,19 +2350,19 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2362,10 +2374,10 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2383,10 +2395,10 @@
         <v>15</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2398,10 +2410,10 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2413,10 +2425,10 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2428,10 +2440,10 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2447,82 +2459,82 @@
         <v>15</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="H30" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="H31" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="H32" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="8:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="H33" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="8:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="H34" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="8:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="H35" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="8:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="H36" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="8:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="H37" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="8:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="H38" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2533,7 +2545,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AMJ25"/>
+  <dimension ref="A1:AMJ44"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="15"/>
@@ -2550,7 +2562,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="16" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -2567,7 +2579,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>8</v>
@@ -2576,10 +2588,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
@@ -2617,38 +2629,43 @@
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="B7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D7" s="1">
         <v>3</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="2"/>
+      <c r="E7" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
@@ -2656,19 +2673,19 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>206</v>
+        <v>44</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>207</v>
+        <v>85</v>
+      </c>
+      <c r="G8" s="1">
+        <v>111</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
@@ -2683,127 +2700,317 @@
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="H10" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="H11" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="H12" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="H13" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="H14" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="H15" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="H16" s="15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I16" s="15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="H17" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="H18" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="H19" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="H20" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="H21" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="H22" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="H23" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27" s="1"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28" s="1"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="H29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="H30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="H31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="H32" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H33" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H34" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H35" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H36" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H37" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H38" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H39" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H40" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H41" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H42" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B44" s="22" t="s">
         <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H17" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H18" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H19" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H20" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H21" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H22" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H23" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B25" s="22" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2836,7 +3043,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="16" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -2862,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -2953,7 +3160,7 @@
     </row>
     <row r="6" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -2982,10 +3189,10 @@
     </row>
     <row r="7" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1">
         <v>7</v>
@@ -2994,70 +3201,70 @@
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -3066,10 +3273,10 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -3096,13 +3303,13 @@
       <c r="D9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
@@ -3162,13 +3369,13 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -3228,13 +3435,13 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -3294,13 +3501,13 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
@@ -3360,13 +3567,13 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="K13" s="1">
         <v>0</v>
@@ -3426,13 +3633,13 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
@@ -3492,13 +3699,13 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -3558,13 +3765,13 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
@@ -3624,13 +3831,13 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>
@@ -3690,13 +3897,13 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -3756,13 +3963,13 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -3822,13 +4029,13 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
@@ -3888,10 +4095,10 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -3920,10 +4127,10 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -3945,15 +4152,15 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A24" s="25" t="s">
-        <v>185</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C25" s="1">
         <v>7</v>
@@ -3962,70 +4169,70 @@
         <v>5</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="M25" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
@@ -4037,10 +4244,10 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -4069,13 +4276,13 @@
       <c r="F27" s="2"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="K27" s="1">
         <v>0</v>
@@ -4135,13 +4342,13 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K28" s="1">
         <v>0</v>
@@ -4201,13 +4408,13 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="K29" s="1">
         <v>0</v>
@@ -4267,13 +4474,13 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
@@ -4333,13 +4540,13 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
@@ -4399,13 +4606,13 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="K32" s="1">
         <v>0</v>
@@ -4465,13 +4672,13 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="K33" s="1">
         <v>0</v>
@@ -4531,13 +4738,13 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
@@ -4597,13 +4804,13 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
@@ -4663,13 +4870,13 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
@@ -4729,13 +4936,13 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="K37" s="1">
         <v>0</v>
@@ -4795,13 +5002,13 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="K38" s="1">
         <v>0</v>
@@ -4861,10 +5068,10 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -4893,10 +5100,10 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -4944,7 +5151,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="16" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -4970,10 +5177,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -5025,10 +5232,10 @@
     </row>
     <row r="6" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1">
         <v>7</v>
@@ -5037,34 +5244,34 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5073,10 +5280,10 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -5091,13 +5298,13 @@
       <c r="D8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
@@ -5121,13 +5328,13 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
@@ -5151,13 +5358,13 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -5181,13 +5388,13 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -5211,13 +5418,13 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
@@ -5241,13 +5448,13 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="K13" s="1">
         <v>0</v>
@@ -5271,13 +5478,13 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
@@ -5301,13 +5508,13 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -5331,13 +5538,13 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
@@ -5361,13 +5568,13 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>
@@ -5391,13 +5598,13 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
@@ -5421,13 +5628,13 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
@@ -5451,10 +5658,10 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -5471,10 +5678,10 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -5509,19 +5716,19 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -5544,10 +5751,10 @@
         <v>15</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -5562,10 +5769,10 @@
       <c r="D25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -5582,10 +5789,10 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -5651,7 +5858,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="16" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5677,10 +5884,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5717,10 +5924,10 @@
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1">
         <v>7</v>
@@ -5729,19 +5936,19 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5750,10 +5957,10 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5763,10 +5970,10 @@
       <c r="D8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5778,10 +5985,10 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5793,10 +6000,10 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5808,10 +6015,10 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5823,10 +6030,10 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5838,10 +6045,10 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5853,10 +6060,10 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5868,10 +6075,10 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5883,10 +6090,10 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5898,10 +6105,10 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5913,10 +6120,10 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5928,10 +6135,10 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5943,10 +6150,10 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5958,10 +6165,10 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -5986,19 +6193,19 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -6016,10 +6223,10 @@
         <v>15</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -6029,10 +6236,10 @@
       <c r="D25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -6044,10 +6251,10 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -6059,10 +6266,10 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -6078,26 +6285,26 @@
         <v>15</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="H29" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="H30" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -6118,7 +6325,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="16" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -6144,10 +6351,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
@@ -6175,7 +6382,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B6" s="15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -6196,7 +6403,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="16" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -6222,10 +6429,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
@@ -6253,7 +6460,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B6" s="15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/T41_V012_Files/T41_V012_Design_Documents/T41_V12.6_I2C_Assignments.xlsx
+++ b/T41_V012_Files/T41_V012_Design_Documents/T41_V12.6_I2C_Assignments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\GitHub\T41\T41_V012_Files\T41_V012_Design_Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bill\Documents\GitHub\T41\T41_V012_Files\T41_V012_Design_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C04B87-7219-47FB-AE81-B9FEE998E55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29CA0D80-91BE-4652-B51B-D52789CA3BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="233">
   <si>
     <t>I2C Addresses For The T41 V012.6</t>
   </si>
@@ -159,9 +159,6 @@
   </si>
   <si>
     <t>0x60</t>
-  </si>
-  <si>
-    <t>Si5351a Frequency Control - Primary Receiver and Transmitter</t>
   </si>
   <si>
     <t>Si5351a Frequency Control - Second Receiver</t>
@@ -747,6 +744,15 @@
   </si>
   <si>
     <t>0x40 or 0x38</t>
+  </si>
+  <si>
+    <t>Si5351a Frequency Control - Primary Receiver and Transmitter for RF board V12.7 and before</t>
+  </si>
+  <si>
+    <t>0x61</t>
+  </si>
+  <si>
+    <t>Si5351a Frequency Control - Primary Receiver and Transmitter for RF board V12.8 and after</t>
   </si>
 </sst>
 </file>
@@ -1279,26 +1285,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ36"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AMJ37"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="8.7265625" style="1"/>
-    <col min="4" max="4" width="16.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="3.90625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.54296875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.453125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.81640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.7265625" style="2" customWidth="1"/>
-    <col min="10" max="1024" width="8.7265625" style="2"/>
+    <col min="1" max="3" width="8.77734375" style="1"/>
+    <col min="4" max="4" width="16.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="3.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.77734375" style="2" customWidth="1"/>
+    <col min="10" max="1024" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="4"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1327,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -1353,7 +1359,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -1366,7 +1372,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
@@ -1374,7 +1380,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>18</v>
@@ -1395,7 +1401,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
@@ -1415,7 +1421,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
@@ -1435,7 +1441,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1446,7 +1452,7 @@
       <c r="H9" s="6"/>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>27</v>
       </c>
@@ -1463,7 +1469,7 @@
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -1473,7 +1479,7 @@
       </c>
       <c r="M10" s="10"/>
     </row>
-    <row r="11" spans="1:13" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1484,7 +1490,7 @@
       <c r="H11" s="6"/>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>29</v>
       </c>
@@ -1513,7 +1519,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>33</v>
       </c>
@@ -1529,7 +1535,7 @@
       </c>
       <c r="M13" s="10"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="D14" s="9"/>
       <c r="G14" s="1" t="s">
@@ -1543,7 +1549,7 @@
       </c>
       <c r="M14" s="10"/>
     </row>
-    <row r="15" spans="1:13" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1554,7 +1560,7 @@
       <c r="H15" s="6"/>
       <c r="M15" s="8"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
@@ -1574,284 +1580,294 @@
         <v>41</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
       <c r="D17" s="9"/>
       <c r="G17" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D18" s="9"/>
       <c r="G18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="1">
-        <v>111</v>
+        <v>227</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D19" s="9"/>
       <c r="G19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="1">
+        <v>111</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D20" s="9"/>
+      <c r="G20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I19" s="2" t="s">
+    </row>
+    <row r="21" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
+      <c r="B22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="1">
+        <v>7</v>
+      </c>
+      <c r="F22" s="1">
+        <v>5</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="H22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="D23" s="9"/>
+      <c r="G23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" s="1">
+        <v>110</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E25" s="1">
         <v>7</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F25" s="1">
         <v>5</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="5"/>
-      <c r="D22" s="9"/>
-      <c r="G22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H22" s="1">
-        <v>110</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="5" t="s">
+      <c r="G25" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="1">
-        <v>7</v>
-      </c>
-      <c r="F24" s="1">
-        <v>5</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>3</v>
-      </c>
-      <c r="G27" s="1" t="s">
+      <c r="I28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I27" s="2" t="s">
+    </row>
+    <row r="29" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="1">
+        <v>7</v>
+      </c>
+      <c r="F30" s="1">
+        <v>5</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="1" t="s">
+      <c r="H30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D33" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E33" s="1">
         <v>7</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F33" s="1">
         <v>5</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="G33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I30" s="2" t="s">
+      <c r="I33" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-    </row>
-    <row r="32" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="1">
-        <v>7</v>
-      </c>
-      <c r="F32" s="1">
-        <v>5</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H32" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="2" t="s">
+      <c r="G34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="I34" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="5" t="s">
+    <row r="35" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="14" t="s">
         <v>69</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H33" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="14" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1863,23 +1879,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AMJ9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="15"/>
-    <col min="2" max="2" width="10.26953125" style="15" customWidth="1"/>
-    <col min="3" max="3" width="3.90625" style="15" customWidth="1"/>
-    <col min="4" max="4" width="4.54296875" style="15" customWidth="1"/>
-    <col min="5" max="8" width="8.7265625" style="15"/>
-    <col min="9" max="9" width="33.7265625" style="15" customWidth="1"/>
-    <col min="10" max="1024" width="8.7265625" style="15"/>
+    <col min="1" max="1" width="8.77734375" style="15"/>
+    <col min="2" max="2" width="10.21875" style="15" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="4.5546875" style="15" customWidth="1"/>
+    <col min="5" max="8" width="8.77734375" style="15"/>
+    <col min="9" max="9" width="33.77734375" style="15" customWidth="1"/>
+    <col min="10" max="1024" width="8.77734375" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -1902,13 +1918,13 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -1931,7 +1947,7 @@
       <c r="H4" s="5"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>24</v>
       </c>
@@ -1945,21 +1961,21 @@
         <v>5</v>
       </c>
       <c r="E6" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="15" t="s">
         <v>74</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>75</v>
       </c>
       <c r="H6" s="18" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="18" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="18" t="s">
-        <v>77</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>26</v>
@@ -1971,18 +1987,18 @@
         <v>5</v>
       </c>
       <c r="E7" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="I7" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="I7" s="15" t="s">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A9" s="20" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1994,27 +2010,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I38"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.08984375" customWidth="1"/>
-    <col min="3" max="3" width="3.90625" customWidth="1"/>
-    <col min="4" max="4" width="4.81640625" customWidth="1"/>
-    <col min="5" max="5" width="4.36328125" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" customWidth="1"/>
-    <col min="7" max="8" width="8.26953125" customWidth="1"/>
-    <col min="9" max="9" width="44.54296875" customWidth="1"/>
-    <col min="10" max="10" width="67.90625" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" customWidth="1"/>
+    <col min="4" max="4" width="4.77734375" customWidth="1"/>
+    <col min="5" max="5" width="4.33203125" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="8" width="8.21875" customWidth="1"/>
+    <col min="9" max="9" width="44.5546875" customWidth="1"/>
+    <col min="10" max="10" width="67.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A2" s="16"/>
     </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -2037,13 +2053,13 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="21" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -2065,7 +2081,7 @@
       </c>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2075,7 +2091,7 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -2092,16 +2108,16 @@
         <v>34</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>84</v>
-      </c>
       <c r="H6" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="9"/>
       <c r="C7" s="1"/>
@@ -2110,31 +2126,31 @@
         <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="9"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="H8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="9"/>
       <c r="C9" s="1"/>
@@ -2143,13 +2159,13 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="9"/>
       <c r="C10" s="1"/>
@@ -2158,13 +2174,13 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="9"/>
       <c r="C11" s="1"/>
@@ -2173,13 +2189,13 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="9"/>
       <c r="C12" s="1"/>
@@ -2188,13 +2204,13 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="9"/>
       <c r="C13" s="1"/>
@@ -2203,13 +2219,13 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="9"/>
       <c r="C14" s="1"/>
@@ -2218,13 +2234,13 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="9"/>
       <c r="C15" s="1"/>
@@ -2233,13 +2249,13 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="9"/>
       <c r="C16" s="1"/>
@@ -2248,13 +2264,13 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="9"/>
       <c r="C17" s="1"/>
@@ -2263,13 +2279,13 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="9"/>
       <c r="C18" s="1"/>
@@ -2278,13 +2294,13 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="9"/>
       <c r="C19" s="1"/>
@@ -2293,13 +2309,13 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="9"/>
       <c r="C20" s="1"/>
@@ -2308,13 +2324,13 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="9"/>
       <c r="C21" s="1"/>
@@ -2323,13 +2339,13 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="9"/>
       <c r="C22" s="1"/>
@@ -2338,34 +2354,34 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="9"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="9"/>
       <c r="C24" s="1"/>
@@ -2374,13 +2390,13 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="9"/>
       <c r="C25" s="1"/>
@@ -2395,13 +2411,13 @@
         <v>15</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="9"/>
       <c r="C26" s="1"/>
@@ -2410,13 +2426,13 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="9"/>
       <c r="C27" s="1"/>
@@ -2425,13 +2441,13 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="9"/>
       <c r="C28" s="1"/>
@@ -2440,13 +2456,13 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="9"/>
       <c r="C29" s="1"/>
@@ -2459,82 +2475,82 @@
         <v>15</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I29" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="H30" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I30" s="2" t="s">
+    <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H31" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="H31" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I31" s="2" t="s">
+    <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H32" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="H32" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I32" s="2" t="s">
+    <row r="33" spans="8:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H33" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="33" spans="8:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="H33" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I33" s="2" t="s">
+    <row r="34" spans="8:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H34" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I34" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="8:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="H34" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I34" s="2" t="s">
+    <row r="35" spans="8:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H35" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="8:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="H35" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I35" s="2" t="s">
+    <row r="36" spans="8:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H36" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="8:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="H36" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I36" s="2" t="s">
+    <row r="37" spans="8:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H37" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I37" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="37" spans="8:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="H37" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I37" s="2" t="s">
+    <row r="38" spans="8:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H38" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I38" s="2" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="38" spans="8:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="H38" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2546,26 +2562,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AMJ44"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="15"/>
-    <col min="2" max="2" width="10.26953125" style="15" customWidth="1"/>
-    <col min="3" max="3" width="3.90625" style="15" customWidth="1"/>
-    <col min="4" max="4" width="4.54296875" style="15" customWidth="1"/>
-    <col min="5" max="5" width="15.54296875" style="15" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="8.6328125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="8.7265625" style="15"/>
-    <col min="9" max="9" width="82.1796875" style="15" customWidth="1"/>
-    <col min="10" max="1024" width="8.7265625" style="15"/>
+    <col min="1" max="1" width="8.77734375" style="15"/>
+    <col min="2" max="2" width="10.21875" style="15" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="4.5546875" style="15" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" style="15" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="15" customWidth="1"/>
+    <col min="8" max="8" width="8.77734375" style="15"/>
+    <col min="9" max="9" width="82.21875" style="15" customWidth="1"/>
+    <col min="10" max="1024" width="8.77734375" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -2579,7 +2595,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>8</v>
@@ -2588,13 +2604,13 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -2617,7 +2633,7 @@
       <c r="H4" s="5"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2628,9 +2644,9 @@
       <c r="H5" s="5"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -2641,7 +2657,7 @@
       <c r="H6" s="5"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -2658,37 +2674,37 @@
         <v>41</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="9"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G8" s="1">
         <v>111</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="9"/>
       <c r="C9" s="1"/>
@@ -2700,127 +2716,127 @@
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I9" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I10" s="15" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I10" s="15" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" s="15" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I11" s="15" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" s="15" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H12" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I12" s="15" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I13" s="15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I13" s="15" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I14" s="15" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H14" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I14" s="15" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H16" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="I16" s="15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H15" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H16" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="I16" s="15" t="s">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H17" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H17" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="I17" s="15" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" s="15" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H18" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="I18" s="15" t="s">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="I19" s="15" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H19" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I19" s="15" t="s">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H20" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I20" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H20" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="I20" s="15" t="s">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H21" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="I21" s="15" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H21" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H22" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H23" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2831,7 +2847,7 @@
       <c r="H25" s="5"/>
       <c r="I25" s="2"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>17</v>
       </c>
@@ -2845,40 +2861,40 @@
         <v>3</v>
       </c>
       <c r="E26" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="I26" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="I26" s="15" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="9"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="H27" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G27" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="I27" s="15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="9"/>
       <c r="C28" s="1"/>
@@ -2890,127 +2906,127 @@
         <v>15</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I28" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I29" s="15" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I29" s="15" t="s">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I30" s="15" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H30" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I30" s="15" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I31" s="15" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H31" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I31" s="15" t="s">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H32" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I32" s="15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="H32" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I32" s="15" t="s">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" s="15" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H33" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I33" s="15" t="s">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H34" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="I35" s="15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H34" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I34" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H35" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="I35" s="15" t="s">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H36" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="I36" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H36" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="I36" s="15" t="s">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I37" s="15" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H37" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="I37" s="15" t="s">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H38" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="I38" s="15" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H38" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I38" s="15" t="s">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H39" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I39" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H39" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="I39" s="15" t="s">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H40" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="I40" s="15" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H40" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="I40" s="15" t="s">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B44" s="22" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H41" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="I41" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H42" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B44" s="22" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3022,31 +3038,31 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Z40"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.26953125" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="3.90625" customWidth="1"/>
-    <col min="4" max="4" width="4.54296875" customWidth="1"/>
-    <col min="5" max="5" width="8.26953125" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" customWidth="1"/>
-    <col min="7" max="7" width="8.26953125" customWidth="1"/>
-    <col min="8" max="8" width="16.7265625" customWidth="1"/>
-    <col min="9" max="9" width="17.81640625" customWidth="1"/>
-    <col min="10" max="10" width="6.90625" style="23" customWidth="1"/>
-    <col min="11" max="11" width="5.54296875" style="23" customWidth="1"/>
-    <col min="12" max="12" width="5.1796875" style="23" customWidth="1"/>
-    <col min="13" max="14" width="5.54296875" style="23" customWidth="1"/>
-    <col min="15" max="18" width="5.6328125" style="23" customWidth="1"/>
-    <col min="19" max="26" width="5.54296875" style="23" customWidth="1"/>
+    <col min="1" max="1" width="6.21875" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" customWidth="1"/>
+    <col min="4" max="4" width="4.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="8.21875" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1"/>
+    <col min="9" max="9" width="17.77734375" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" style="23" customWidth="1"/>
+    <col min="11" max="11" width="5.5546875" style="23" customWidth="1"/>
+    <col min="12" max="12" width="5.21875" style="23" customWidth="1"/>
+    <col min="13" max="14" width="5.5546875" style="23" customWidth="1"/>
+    <col min="15" max="18" width="5.6640625" style="23" customWidth="1"/>
+    <col min="19" max="26" width="5.5546875" style="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:26" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -3069,10 +3085,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>72</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>73</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -3092,7 +3108,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -3131,7 +3147,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -3158,9 +3174,9 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -3187,7 +3203,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -3201,82 +3217,82 @@
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="I7" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="9"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -3296,20 +3312,20 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="9"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
@@ -3360,7 +3376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="9"/>
       <c r="C10" s="1"/>
@@ -3369,13 +3385,13 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -3426,7 +3442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="9"/>
       <c r="C11" s="1"/>
@@ -3435,13 +3451,13 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -3492,7 +3508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="9"/>
       <c r="C12" s="1"/>
@@ -3501,13 +3517,13 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
@@ -3558,7 +3574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="9"/>
       <c r="C13" s="1"/>
@@ -3567,13 +3583,13 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K13" s="1">
         <v>0</v>
@@ -3624,7 +3640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="9"/>
       <c r="C14" s="1"/>
@@ -3633,13 +3649,13 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
@@ -3690,7 +3706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="9"/>
       <c r="C15" s="1"/>
@@ -3699,13 +3715,13 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -3756,7 +3772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="9"/>
       <c r="C16" s="1"/>
@@ -3765,13 +3781,13 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I16" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
@@ -3822,7 +3838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="9"/>
       <c r="C17" s="1"/>
@@ -3831,13 +3847,13 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I17" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>
@@ -3888,7 +3904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="9"/>
       <c r="C18" s="1"/>
@@ -3897,13 +3913,13 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I18" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -3954,7 +3970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="9"/>
       <c r="C19" s="1"/>
@@ -3963,13 +3979,13 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -4020,7 +4036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="9"/>
       <c r="C20" s="1"/>
@@ -4029,13 +4045,13 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I20" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
@@ -4086,7 +4102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="9"/>
       <c r="C21" s="1"/>
@@ -4095,10 +4111,10 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -4118,7 +4134,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="9"/>
       <c r="C22" s="1"/>
@@ -4127,10 +4143,10 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -4150,12 +4166,12 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -4169,73 +4185,73 @@
         <v>5</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="I25" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="K25" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="9"/>
       <c r="C26" s="1"/>
@@ -4244,10 +4260,10 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -4267,7 +4283,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="9"/>
       <c r="C27" s="1"/>
@@ -4276,13 +4292,13 @@
       <c r="F27" s="2"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I27" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="K27" s="1">
         <v>0</v>
@@ -4333,7 +4349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="9"/>
       <c r="C28" s="1"/>
@@ -4342,13 +4358,13 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I28" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="K28" s="1">
         <v>0</v>
@@ -4399,7 +4415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="9"/>
       <c r="C29" s="1"/>
@@ -4408,13 +4424,13 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K29" s="1">
         <v>0</v>
@@ -4465,7 +4481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="9"/>
       <c r="C30" s="1"/>
@@ -4474,13 +4490,13 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
@@ -4531,7 +4547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="9"/>
       <c r="C31" s="1"/>
@@ -4540,13 +4556,13 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
@@ -4597,7 +4613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="9"/>
       <c r="C32" s="1"/>
@@ -4606,13 +4622,13 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K32" s="1">
         <v>0</v>
@@ -4663,7 +4679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="9"/>
       <c r="C33" s="1"/>
@@ -4672,13 +4688,13 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I33" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="K33" s="1">
         <v>0</v>
@@ -4729,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="9"/>
       <c r="C34" s="1"/>
@@ -4738,13 +4754,13 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I34" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
@@ -4795,7 +4811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="9"/>
       <c r="C35" s="1"/>
@@ -4804,13 +4820,13 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I35" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
@@ -4861,7 +4877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="9"/>
       <c r="C36" s="1"/>
@@ -4870,13 +4886,13 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I36" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
@@ -4927,7 +4943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="9"/>
       <c r="C37" s="1"/>
@@ -4936,13 +4952,13 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I37" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="K37" s="1">
         <v>0</v>
@@ -4993,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="9"/>
       <c r="C38" s="1"/>
@@ -5002,13 +5018,13 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I38" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="K38" s="1">
         <v>0</v>
@@ -5059,7 +5075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="9"/>
       <c r="C39" s="1"/>
@@ -5068,10 +5084,10 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -5091,7 +5107,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="9"/>
       <c r="C40" s="1"/>
@@ -5100,10 +5116,10 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -5132,29 +5148,29 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.26953125" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="3.90625" customWidth="1"/>
-    <col min="4" max="4" width="4.54296875" customWidth="1"/>
+    <col min="1" max="1" width="6.21875" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" customWidth="1"/>
+    <col min="4" max="4" width="4.5546875" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="16.7265625" customWidth="1"/>
-    <col min="9" max="9" width="67.90625" customWidth="1"/>
-    <col min="10" max="10" width="6.90625" style="23" customWidth="1"/>
-    <col min="11" max="11" width="5.54296875" style="23" customWidth="1"/>
-    <col min="12" max="12" width="5.1796875" style="23" customWidth="1"/>
-    <col min="13" max="14" width="5.54296875" style="23" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1"/>
+    <col min="9" max="9" width="67.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" style="23" customWidth="1"/>
+    <col min="11" max="11" width="5.5546875" style="23" customWidth="1"/>
+    <col min="12" max="12" width="5.21875" style="23" customWidth="1"/>
+    <col min="13" max="14" width="5.5546875" style="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:14" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -5177,10 +5193,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>72</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>73</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -5188,7 +5204,7 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -5215,7 +5231,7 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -5230,7 +5246,7 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -5244,46 +5260,46 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="9"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -5291,20 +5307,20 @@
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="9"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
@@ -5319,7 +5335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="9"/>
       <c r="C9" s="1"/>
@@ -5328,13 +5344,13 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
@@ -5349,7 +5365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="9"/>
       <c r="C10" s="1"/>
@@ -5358,13 +5374,13 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -5379,7 +5395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="9"/>
       <c r="C11" s="1"/>
@@ -5388,13 +5404,13 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -5409,7 +5425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="9"/>
       <c r="C12" s="1"/>
@@ -5418,13 +5434,13 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
@@ -5439,7 +5455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="9"/>
       <c r="C13" s="1"/>
@@ -5448,13 +5464,13 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K13" s="1">
         <v>0</v>
@@ -5469,7 +5485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="9"/>
       <c r="C14" s="1"/>
@@ -5478,13 +5494,13 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
@@ -5499,7 +5515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="9"/>
       <c r="C15" s="1"/>
@@ -5508,13 +5524,13 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -5529,7 +5545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="9"/>
       <c r="C16" s="1"/>
@@ -5538,13 +5554,13 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
@@ -5559,7 +5575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="9"/>
       <c r="C17" s="1"/>
@@ -5568,13 +5584,13 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>
@@ -5589,7 +5605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="9"/>
       <c r="C18" s="1"/>
@@ -5598,13 +5614,13 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
@@ -5619,7 +5635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="9"/>
       <c r="C19" s="1"/>
@@ -5628,13 +5644,13 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
@@ -5649,7 +5665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="9"/>
       <c r="C20" s="1"/>
@@ -5658,10 +5674,10 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -5669,7 +5685,7 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="9"/>
       <c r="C21" s="1"/>
@@ -5678,10 +5694,10 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -5689,7 +5705,7 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="9"/>
       <c r="C22" s="1"/>
@@ -5710,25 +5726,25 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="9"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -5736,7 +5752,7 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="9"/>
       <c r="C24" s="1"/>
@@ -5751,10 +5767,10 @@
         <v>15</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -5762,17 +5778,17 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="9"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -5780,7 +5796,7 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="9"/>
       <c r="C26" s="1"/>
@@ -5789,10 +5805,10 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -5800,7 +5816,7 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="9"/>
       <c r="C27" s="1"/>
@@ -5815,7 +5831,7 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="9"/>
       <c r="C28" s="1"/>
@@ -5843,25 +5859,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.26953125" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
-    <col min="3" max="3" width="3.90625" customWidth="1"/>
-    <col min="4" max="4" width="4.54296875" customWidth="1"/>
+    <col min="1" max="1" width="6.21875" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" customWidth="1"/>
+    <col min="4" max="4" width="4.5546875" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="16.7265625" customWidth="1"/>
-    <col min="9" max="9" width="37.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1"/>
+    <col min="9" max="9" width="37.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -5884,13 +5900,13 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -5912,7 +5928,7 @@
       </c>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -5922,7 +5938,7 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -5939,44 +5955,44 @@
         <v>34</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G6" s="26" t="s">
         <v>35</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="9"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="9"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="9"/>
       <c r="C9" s="1"/>
@@ -5985,13 +6001,13 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="9"/>
       <c r="C10" s="1"/>
@@ -6000,13 +6016,13 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="9"/>
       <c r="C11" s="1"/>
@@ -6015,13 +6031,13 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="9"/>
       <c r="C12" s="1"/>
@@ -6030,13 +6046,13 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="9"/>
       <c r="C13" s="1"/>
@@ -6045,13 +6061,13 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="9"/>
       <c r="C14" s="1"/>
@@ -6060,13 +6076,13 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="9"/>
       <c r="C15" s="1"/>
@@ -6075,13 +6091,13 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="9"/>
       <c r="C16" s="1"/>
@@ -6090,13 +6106,13 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="9"/>
       <c r="C17" s="1"/>
@@ -6105,13 +6121,13 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="9"/>
       <c r="C18" s="1"/>
@@ -6120,13 +6136,13 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="9"/>
       <c r="C19" s="1"/>
@@ -6135,13 +6151,13 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="9"/>
       <c r="C20" s="1"/>
@@ -6150,13 +6166,13 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="9"/>
       <c r="C21" s="1"/>
@@ -6165,13 +6181,13 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="9"/>
       <c r="C22" s="1"/>
@@ -6187,28 +6203,28 @@
       </c>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="9"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>38</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="9"/>
       <c r="C24" s="1"/>
@@ -6223,26 +6239,26 @@
         <v>15</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="9"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="9"/>
       <c r="C26" s="1"/>
@@ -6251,13 +6267,13 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="9"/>
       <c r="C27" s="1"/>
@@ -6266,13 +6282,13 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="9"/>
       <c r="C28" s="1"/>
@@ -6285,26 +6301,26 @@
         <v>15</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H29" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H30" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -6316,19 +6332,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AMJ6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="15"/>
-    <col min="2" max="2" width="10.26953125" style="15" customWidth="1"/>
-    <col min="3" max="1024" width="8.7265625" style="15"/>
+    <col min="1" max="1" width="8.77734375" style="15"/>
+    <col min="2" max="2" width="10.21875" style="15" customWidth="1"/>
+    <col min="3" max="1024" width="8.77734375" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -6351,13 +6367,13 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -6380,9 +6396,9 @@
       <c r="H4" s="5"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -6394,19 +6410,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AMJ6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="15"/>
-    <col min="2" max="2" width="10.26953125" style="15" customWidth="1"/>
-    <col min="3" max="1024" width="8.7265625" style="15"/>
+    <col min="1" max="1" width="8.77734375" style="15"/>
+    <col min="2" max="2" width="10.21875" style="15" customWidth="1"/>
+    <col min="3" max="1024" width="8.77734375" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -6429,13 +6445,13 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -6458,9 +6474,9 @@
       <c r="H4" s="5"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/T41_V012_Files/T41_V012_Design_Documents/T41_V12.6_I2C_Assignments.xlsx
+++ b/T41_V012_Files/T41_V012_Design_Documents/T41_V12.6_I2C_Assignments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bill\Documents\GitHub\T41\T41_V012_Files\T41_V012_Design_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29CA0D80-91BE-4652-B51B-D52789CA3BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F250C527-0D1E-4443-B808-A27ADC2BD7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="235">
   <si>
     <t>I2C Addresses For The T41 V012.6</t>
   </si>
@@ -159,9 +159,6 @@
   </si>
   <si>
     <t>0x60</t>
-  </si>
-  <si>
-    <t>Si5351a Frequency Control - Second Receiver</t>
   </si>
   <si>
     <t>0x27</t>
@@ -753,6 +750,15 @@
   </si>
   <si>
     <t>Si5351a Frequency Control - Primary Receiver and Transmitter for RF board V12.8 and after</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0x6F</t>
+  </si>
+  <si>
+    <t>Si5351a Frequency Control - Second Receiver for RF board V12.7 and before</t>
+  </si>
+  <si>
+    <t>Si5351a Frequency Control - Second Receiver for RF board V12.8 and after</t>
   </si>
 </sst>
 </file>
@@ -1285,7 +1291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ37"/>
+  <dimension ref="A1:AMJ38"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="8.77734375" style="1"/>
@@ -1380,7 +1386,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>18</v>
@@ -1469,7 +1475,7 @@
         <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>15</v>
@@ -1580,294 +1586,303 @@
         <v>41</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="D17" s="9"/>
       <c r="G17" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D18" s="9"/>
       <c r="G18" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>42</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D19" s="9"/>
       <c r="G19" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="1">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>44</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D20" s="9"/>
       <c r="G20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="1">
+        <v>111</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D21" s="9"/>
+      <c r="G21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I20" s="2" t="s">
+    </row>
+    <row r="22" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="1">
+        <v>7</v>
+      </c>
+      <c r="F23" s="1">
+        <v>5</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="1">
-        <v>7</v>
-      </c>
-      <c r="F22" s="1">
-        <v>5</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I23" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I22" s="2" t="s">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="D24" s="9"/>
+      <c r="G24" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="D23" s="9"/>
-      <c r="G23" s="1" t="s">
+      <c r="H24" s="1">
+        <v>110</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H23" s="1">
-        <v>110</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="1">
-        <v>7</v>
-      </c>
-      <c r="F25" s="1">
-        <v>5</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>196</v>
-      </c>
+    </row>
+    <row r="25" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="1">
+        <v>7</v>
+      </c>
+      <c r="F26" s="1">
+        <v>5</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
+        <v>3</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>3</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="I29" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="1">
-        <v>7</v>
-      </c>
-      <c r="F30" s="1">
-        <v>5</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>64</v>
-      </c>
+    </row>
+    <row r="30" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="1">
+        <v>7</v>
+      </c>
+      <c r="F31" s="1">
+        <v>5</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="I32" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I31" s="2" t="s">
+    </row>
+    <row r="33" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="1">
+        <v>7</v>
+      </c>
+      <c r="F34" s="1">
+        <v>5</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H34" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="1">
-        <v>7</v>
-      </c>
-      <c r="F33" s="1">
-        <v>5</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="I33" s="2" t="s">
+      <c r="G35" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H35" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
+    <row r="36" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="14" t="s">
         <v>68</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H34" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1892,7 +1907,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -1918,10 +1933,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>71</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -1961,21 +1976,21 @@
         <v>5</v>
       </c>
       <c r="E6" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="15" t="s">
         <v>73</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>74</v>
       </c>
       <c r="H6" s="18" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>26</v>
@@ -1987,18 +2002,18 @@
         <v>5</v>
       </c>
       <c r="E7" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="I7" s="15" t="s">
         <v>78</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2024,7 +2039,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
@@ -2053,10 +2068,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="21" t="s">
         <v>71</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2108,13 +2123,13 @@
         <v>34</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>83</v>
-      </c>
       <c r="H6" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2126,16 +2141,16 @@
         <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2144,10 +2159,10 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="H8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2159,10 +2174,10 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2174,10 +2189,10 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2189,10 +2204,10 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2204,10 +2219,10 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2219,10 +2234,10 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2234,10 +2249,10 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2249,10 +2264,10 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2264,10 +2279,10 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2279,10 +2294,10 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2294,10 +2309,10 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2309,10 +2324,10 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2324,10 +2339,10 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2339,10 +2354,10 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2354,10 +2369,10 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2366,19 +2381,19 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2390,10 +2405,10 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2411,10 +2426,10 @@
         <v>15</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2426,10 +2441,10 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2441,10 +2456,10 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2456,10 +2471,10 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -2475,82 +2490,82 @@
         <v>15</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H30" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H31" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H32" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="8:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H33" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="8:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H34" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="8:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H35" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="8:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H36" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="8:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H37" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="8:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H38" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2578,7 +2593,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -2595,7 +2610,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>8</v>
@@ -2604,10 +2619,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>71</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -2646,7 +2661,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -2674,13 +2689,13 @@
         <v>41</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -2689,19 +2704,19 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G8" s="1">
         <v>111</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -2716,127 +2731,127 @@
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H10" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H11" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H12" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H13" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H14" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H15" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H16" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H17" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H18" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H19" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H20" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H21" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H22" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H23" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2861,16 +2876,16 @@
         <v>3</v>
       </c>
       <c r="E26" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="I26" s="15" t="s">
         <v>227</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="I26" s="15" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
@@ -2879,19 +2894,19 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="H27" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G27" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="I27" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
@@ -2906,127 +2921,127 @@
         <v>15</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I28" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H29" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H30" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H31" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H32" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H33" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H34" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H35" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H36" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H37" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H38" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H39" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H40" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H41" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H42" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I42" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44" s="22" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3059,7 +3074,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -3085,10 +3100,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>71</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>72</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -3176,7 +3191,7 @@
     </row>
     <row r="6" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -3217,70 +3232,70 @@
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="I7" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:26" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -3289,10 +3304,10 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -3319,13 +3334,13 @@
       <c r="D9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
@@ -3385,13 +3400,13 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -3451,13 +3466,13 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -3517,13 +3532,13 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
@@ -3583,13 +3598,13 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K13" s="1">
         <v>0</v>
@@ -3649,13 +3664,13 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
@@ -3715,13 +3730,13 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -3781,13 +3796,13 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
@@ -3847,13 +3862,13 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I17" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>
@@ -3913,13 +3928,13 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I18" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -3979,13 +3994,13 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I19" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -4045,13 +4060,13 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I20" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
@@ -4111,10 +4126,10 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -4143,10 +4158,10 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -4168,7 +4183,7 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
@@ -4185,70 +4200,70 @@
         <v>5</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="I25" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="K25" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
@@ -4260,10 +4275,10 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -4292,13 +4307,13 @@
       <c r="F27" s="2"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I27" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="K27" s="1">
         <v>0</v>
@@ -4358,13 +4373,13 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I28" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="K28" s="1">
         <v>0</v>
@@ -4424,13 +4439,13 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K29" s="1">
         <v>0</v>
@@ -4490,13 +4505,13 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
@@ -4556,13 +4571,13 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
@@ -4622,13 +4637,13 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K32" s="1">
         <v>0</v>
@@ -4688,13 +4703,13 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I33" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="K33" s="1">
         <v>0</v>
@@ -4754,13 +4769,13 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I34" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
@@ -4820,13 +4835,13 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I35" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
@@ -4886,13 +4901,13 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I36" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
@@ -4952,13 +4967,13 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I37" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="K37" s="1">
         <v>0</v>
@@ -5018,13 +5033,13 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I38" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="K38" s="1">
         <v>0</v>
@@ -5084,10 +5099,10 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -5116,10 +5131,10 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -5167,7 +5182,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -5193,10 +5208,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>71</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>72</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -5260,34 +5275,34 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -5296,10 +5311,10 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -5314,13 +5329,13 @@
       <c r="D8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
@@ -5344,13 +5359,13 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
@@ -5374,13 +5389,13 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -5404,13 +5419,13 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -5434,13 +5449,13 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
@@ -5464,13 +5479,13 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K13" s="1">
         <v>0</v>
@@ -5494,13 +5509,13 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
@@ -5524,13 +5539,13 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -5554,13 +5569,13 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
@@ -5584,13 +5599,13 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>
@@ -5614,13 +5629,13 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
@@ -5644,13 +5659,13 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
@@ -5674,10 +5689,10 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -5694,10 +5709,10 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -5732,19 +5747,19 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -5767,10 +5782,10 @@
         <v>15</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -5785,10 +5800,10 @@
       <c r="D25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -5805,10 +5820,10 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -5874,7 +5889,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -5900,10 +5915,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>71</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -5955,16 +5970,16 @@
         <v>34</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G6" s="26" t="s">
         <v>35</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -5973,10 +5988,10 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -5986,10 +6001,10 @@
       <c r="D8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6001,10 +6016,10 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6016,10 +6031,10 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6031,10 +6046,10 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6046,10 +6061,10 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6061,10 +6076,10 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6076,10 +6091,10 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6091,10 +6106,10 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6106,10 +6121,10 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6121,10 +6136,10 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6136,10 +6151,10 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6151,10 +6166,10 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6166,10 +6181,10 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6181,10 +6196,10 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6209,19 +6224,19 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>38</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6239,10 +6254,10 @@
         <v>15</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6252,10 +6267,10 @@
       <c r="D25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6267,10 +6282,10 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6282,10 +6297,10 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -6301,26 +6316,26 @@
         <v>15</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H29" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="H30" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -6341,7 +6356,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -6367,10 +6382,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>71</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -6398,7 +6413,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -6419,7 +6434,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -6445,10 +6460,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>71</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -6476,7 +6491,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
